--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify user login with valid email and password credentials</t>
+          <t>Valid Email Password Login Authentication Flow</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify error message on login with invalid password</t>
+          <t>Invalid Password Submission Error Alert Handling</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify error message on login with unregistered email address</t>
+          <t>Unregistered Email Account Rejection Message</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify email input field syntax validation with missing @ domain</t>
+          <t>Email Syntax Validation Rule (@ Domain Filter)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify password masking toggle button reveals plain text password</t>
+          <t>Password Masking Visibility Eye Icon Toggle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify 'Remember Me' checkbox persists session token across browser restart</t>
+          <t>'Remember Me' Session Persistence Across Browser Restart</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Google OAuth2 single sign-on redirect flow</t>
+          <t>Google OAuth2 Single Sign-On Authentication Redirection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify GitHub OAuth2 single sign-on authentication callback</t>
+          <t>GitHub OAuth2 Callback Authorization Pipeline</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify password reset request sends verification email link</t>
+          <t>Password Reset Email Verification Link Dispatch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify password reset token expiration after 15 minutes</t>
+          <t>Password Reset Token Expiration Lifecycle (15-Min)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify new password strength meter updates on user input</t>
+          <t>Dynamic Password Strength Indicator Meter Update</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify user registration form submission with valid details</t>
+          <t>New Account User Registration Form Submission</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify duplicate email registration returns 409 conflict message</t>
+          <t>Duplicate Account Email Conflict Rejection (409)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify Terms of Service checkbox mandatory check on signup</t>
+          <t>Mandatory Terms of Service Checkbox Requirement</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify Privacy Policy hyperlink opens in new browser tab</t>
+          <t>Privacy Policy External Hyperlink New Tab Launch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify automatic logout after 30 minutes of user inactivity</t>
+          <t>Automatic Session Timeout After 30 Minutes Inactivity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify manual user logout revokes JWT token and redirects to login</t>
+          <t>Manual Logout Revocation of JWT Token</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify multi-factor authentication (MFA) OTP prompt display</t>
+          <t>Multi-Factor Authentication (MFA) OTP Input Screen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify MFA invalid 6-digit OTP rejection message</t>
+          <t>MFA Invalid 6-Digit OTP Error Rejection</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify MFA fallback recovery code verification</t>
+          <t>MFA Backup Recovery Code Verification Sequence</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify account lockout after 5 consecutive failed login attempts</t>
+          <t>Account Lockout Enforcement After 5 Failed Logins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify CAPTCHA challenge trigger on suspicious IP login attempt</t>
+          <t>CAPTCHA Challenge Trigger on Suspicious IP Origin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify session token refresh API call before expiration</t>
+          <t>JWT Session Bearer Token Auto-Refresh Header</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify concurrent login attempt invalidates older session token</t>
+          <t>Concurrent Active Session Invalidation Handling</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify XSS injection payload in login email field is sanitized</t>
+          <t>XSS Injection Sanitization in Login Input Fields</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify standard user cannot access /admin/dashboard route</t>
+          <t>Standard User Route Access Restriction (/admin)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify admin user can access system configuration panel</t>
+          <t>Admin Role Access Permission to System Panel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify unauthorized API request returns HTTP 401 Unauthorized status</t>
+          <t>Unauthenticated Request Response Code (401 Unauthorized)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify forbidden resource request returns HTTP 403 Forbidden page</t>
+          <t>Forbidden Resource Access Response (403 Forbidden)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify role-based action button visibility for Manager role</t>
+          <t>Manager Role Custom Action Button Render</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify read-only user cannot submit POST/PUT posture analysis requests</t>
+          <t>Read-Only User Write Operation Rejection (POST/PUT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify user cannot view another user's private posture session history</t>
+          <t>Private Session History Cross-User Access Isolation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify tenant isolation in multi-tenant enterprise dashboard</t>
+          <t>Multi-Tenant Enterprise Workspace Data Boundary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify JWT bearer token header validation on protected endpoints</t>
+          <t>JWT Bearer Token Header Injection Verification</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify tampered JWT signature is rejected by backend gateway</t>
+          <t>Tampered JWT Cryptographic Signature Rejection</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify expired JWT token triggers automatic re-authentication prompt</t>
+          <t>Expired Token Automatic Re-Authentication Dialog</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify API key authentication for external posture telemetry ingestion</t>
+          <t>API Key Authentication for Telemetry Ingestion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify revoked API key fails authentication instantly</t>
+          <t>Revoked API Key Gateway Connection Drop</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verify RBAC permission matrix for posture report deletion</t>
+          <t>RBAC Matrix Enforcement on Posture Record Delete</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verify missing authorization header returns proper JSON error body</t>
+          <t>Missing Auth Header JSON Error Schema Output</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verify session hijacking prevention via IP and User-Agent binding</t>
+          <t>Session Hijacking Prevention via IP/User-Agent Binding</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verify password change invalidates all existing active sessions</t>
+          <t>Global Session Invalidation on Password Change</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verify administrative user impersonation audit logging</t>
+          <t>Admin Impersonation Audit Log Event Dispatcher</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verify privilege escalation payload via URL parameter tampering fails</t>
+          <t>Privilege Escalation Parameter Tampering Block</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verify browser webcam permission request dialog on calibration page</t>
+          <t>Webcam Browser Permission Dialog Prompt Display</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verify camera feed preview canvas renders live video frames</t>
+          <t>Live Video Stream HTML5 Canvas Frame Preview</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verify MediaPipe 33 landmark skeleton overlay renders over live video</t>
+          <t>MediaPipe 33 Landmark Pose Overlay Layer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verify shoulder alignment baseline angle calculation during setup</t>
+          <t>Shoulder Alignment Baseline Calculation Metric</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verify ear-to-shoulder cervical spine distance measurement calibration</t>
+          <t>Ear-to-Shoulder Cervical Spine Distance Gauge</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verify torso slouch angle threshold slider adjusts sensitivity</t>
+          <t>Slouch Sensitivity Threshold Slider Tuning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verify user posture baseline save button updates backend profile</t>
+          <t>Posture Calibration Baseline Profile Update</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verify webcam disconnection triggers visual reconnect alert banner</t>
+          <t>Webcam Disconnect Reconnection Banner Trigger</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verify low-light environment warning prompt displays on canvas</t>
+          <t>Low-Ambient Lighting Environment Alert Badge</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verify multiple person detection warning alert on calibration stream</t>
+          <t>Multiple Pose Detection Warning Banner on Canvas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verify camera resolution toggle switches between 720p and 1080p</t>
+          <t>Camera Stream Resolution Switcher (720p/1080p)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verify frame rate monitor displays real-time FPS metric (24-60 FPS)</t>
+          <t>Real-Time FPS Counter Rendering (24-60 FPS)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verify mirror video view toggle flips video horizontal axis</t>
+          <t>Mirror Video View Horizontal Flip Toggle</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 1 posture position guide</t>
+          <t>Calibration Wizard Step 1 Alignment Guide</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 2 distance from camera check</t>
+          <t>Calibration Wizard Step 2 Camera Distance Check</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verify posture calibration wizard step 3 side view neck angle test</t>
+          <t>Calibration Wizard Step 3 Neck Angle Measurement</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verify posture calibration reset button clears previous baseline data</t>
+          <t>Reset Posture Baseline Button Action Handler</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verify posture score index updates live from 0 to 100 based on posture</t>
+          <t>Live Posture Score Gauge Animation (0-100)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verify green color indicator ring when posture is within 5% tolerance</t>
+          <t>Green Indicator Ring for Ideal Posture Tolerance</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verify amber color indicator ring when mild slouching is detected</t>
+          <t>Amber Indicator Ring for Mild Slouch Warning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verify red color indicator ring when severe slouching exceeds 15 deg</t>
+          <t>Red Indicator Ring for Severe Slouching Alert</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verify posture audio chime toggle button silences posture alerts</t>
+          <t>Posture Audio Chime Alert Mute Control</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verify desktop notification permission prompt on posture slouch alert</t>
+          <t>Desktop Web Push Notification Permission Request</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verify landmark visibility confidence score threshold filter (&gt;0.8)</t>
+          <t>Landmark Confidence Threshold Filter (&gt;0.80)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verify camera device selection dropdown switches active webcams</t>
+          <t>Camera Device Dropdown Switcher Selection</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verify calibration timeout after 3 minutes of uncalibrated video</t>
+          <t>Uncalibrated Video Stream Auto-Timeout (3 Mins)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verify post-calibration summary modal displays baseline metrics</t>
+          <t>Post-Calibration Summary Modal Metric Render</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verify posture calibration data export to JSON file</t>
+          <t>Posture Baseline Metric Data Export to JSON</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verify WebGL hardware acceleration check before MediaPipe init</t>
+          <t>WebGL Hardware Context Check Before Engine Init</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verify WebRTC video stream failure fallback to periodic image snapshot</t>
+          <t>WebRTC Stream Fallback to Image Snapshot Mode</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verify WebSocket connection handshake to /ws/posture endpoint</t>
+          <t>WebSocket Handshake Connection to /ws/posture</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verify live frame landmark coordinates payload structure</t>
+          <t>Live Landmark Coordinate JSON Payload Format</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verify real-time posture score push updates received every 200ms</t>
+          <t>Real-Time Posture Score Push Updates (200ms Interval)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verify automatic WebSocket connection heartbeat ping/pong every 30s</t>
+          <t>WebSocket Keep-Alive Ping/Pong Heartbeat Check</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verify WebSocket reconnection retry backoff strategy on network drop</t>
+          <t>WebSocket Reconnection Exponential Backoff Logic</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verify live session pause button suspends telemetry transmission</t>
+          <t>Live Tracking Session Pause Button Action</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verify live session resume button restarts telemetry transmission</t>
+          <t>Live Tracking Session Resume Button Action</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verify live session stop button finalizes session and saves summary</t>
+          <t>Live Tracking Session Stop and Save Final Summary</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verify session timer ticker increments continuously during live stream</t>
+          <t>Active Session Clock Timer Increment Ticker</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verify real-time posture alert sound effect triggers on red status</t>
+          <t>Audio Sound Alert Trigger on Red Posture Status</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verify browser tab focus change pauses video frame rendering to save CPU</t>
+          <t>Background Tab Inactivity Frame Rendering Throttle</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verify browser tab refocus resumes video frame rendering seamlessly</t>
+          <t>Foreground Tab Focus Motion Resume Handler</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verify live telemetry dashboard latency gauge stays below 100ms</t>
+          <t>Telemetry Transmission Latency Gauge (&lt;100ms)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verify telemetry packet loss recovery handling on dropped frames</t>
+          <t>Packet Loss Recovery Handler for Dropped Frames</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verify live telemetry data encryption over TLS (WSS protocol)</t>
+          <t>TLS Encryption Security Validation on WSS Protocol</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verify total posture monitoring active time counter accuracy</t>
+          <t>Total Active Monitoring Counter Precision Test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verify peak slouch duration highlight overlay on live timeline</t>
+          <t>Peak Slouch Timestamp Highlighter on Timeline</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verify real-time neck angle telemetry chart rendering</t>
+          <t>Real-Time Neck Angle Curve Chart Renderer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Verify real-time shoulder tilt telemetry chart rendering</t>
+          <t>Real-Time Shoulder Tilt Differential Graph</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verify live session notes input box saves user annotations</t>
+          <t>Live Annotation Session Notes Text Area Save</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Verify posture session goal progress bar updates dynamically</t>
+          <t>Daily Posture Goal Radial Progress Bar Update</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verify emergency stop button immediately kills webcam stream</t>
+          <t>Emergency Kill-Switch Button Stream Termination</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Verify streaming data bandwidth usage meter under 500 KB/s</t>
+          <t>Bandwidth Data Usage Meter (&lt;500 KB/s Threshold)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Verify live stream error boundary component captures unexpected JS crashes</t>
+          <t>JS Global Error Boundary Handler on Canvas Crash</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Verify daily posture score average KPI card value calculation</t>
+          <t>Daily Posture Score Average KPI Card Calculation</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Verify total slouch incidents KPI card value calculation</t>
+          <t>Total Slouch Incidents Count Metric Display</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Verify active monitoring duration KPI card display in hours/minutes</t>
+          <t>Active Tracking Duration KPI Card (Hours/Mins)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Verify posture health grade badge (A+, A, B, C, F) logic</t>
+          <t>Posture Health Letter Grade Badge Logic (A+ to F)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verify weekly posture trend line chart renders 7 data points</t>
+          <t>Weekly Posture Trend Line Graph (7-Day Metric)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verify monthly posture distribution pie chart segment calculations</t>
+          <t>Monthly Posture Distribution Segment Breakdown</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Verify hourly slouch frequency bar chart interactive tooltips</t>
+          <t>Hourly Slouch Frequency Bar Chart Tooltip Interactivity</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verify posture score vs break frequency scatter plot chart rendering</t>
+          <t>Posture Score vs Rest Break Scatter Plot Render</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verify date range picker filters analytics between start and end dates</t>
+          <t>Date Range Picker Data Filter Application</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Verify 'Today' quick filter preset sets date filter to current date</t>
+          <t>'Today' Quick Filter Date Preset Action</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Verify 'Last 7 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 7 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verify 'Last 30 Days' quick filter preset updates dashboard widgets</t>
+          <t>'Last 30 Days' Preset Dashboard Metrics Refresh</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Verify 'Custom Range' date picker modal input validation</t>
+          <t>Custom Date Picker Input Validation Safeguard</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Verify analytics refresh button reloads latest backend metrics</t>
+          <t>Manual Refresh Button API Re-fetch Trigger</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Verify posture streak widget displays consecutive good posture days</t>
+          <t>Consecutive Good Posture Streak Day Counter</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Verify posture improvement percentage metric comparison with prior week</t>
+          <t>Weekly Posture Improvement Percentage Comparison</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Verify ergonomics tip of the day card rendering</t>
+          <t>Daily Ergonomic Wellness Recommendation Banner</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verify posture goal progress circular indicator accuracy</t>
+          <t>Target Posture Goal Circular Completion Bar</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Verify worst posture hour of the day highlight alert card</t>
+          <t>Worst Posture Hour Highlight Alert Card</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Verify best posture hour of the day highlight alert card</t>
+          <t>Best Posture Hour Highlight Recognition Card</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Verify posture comparison benchmark with community average</t>
+          <t>Community Posture Score Benchmark Comparison</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Verify dashboard widget drag-and-drop reordering functionality</t>
+          <t>Dashboard Widget Grid Drag-and-Drop Layout</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Verify dashboard widget collapse/expand toggle buttons</t>
+          <t>Dashboard Widget Expand and Collapse Toggle</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Verify posture analytics CSV data export button triggers download</t>
+          <t>Analytics CSV File Data Download Action</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Verify posture analytics Excel data export button triggers download</t>
+          <t>Analytics Excel Workbook Download Action</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Verify dashboard full screen mode button expands view to 100vw</t>
+          <t>Full Screen Mode Viewport Expansion Toggle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Verify posture health risk advisory alert banner for low scores (&lt;50)</t>
+          <t>Health Risk Advisory Banner for Scores Below 50</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Verify dashboard loading skeleton shimmer state while fetching API</t>
+          <t>Dashboard Loading Skeleton Shimmer State Render</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Verify empty state message on dashboard when no session data exists</t>
+          <t>Empty Dashboard Graphic State for New Accounts</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Verify session history data table displays chronologically descending</t>
+          <t>Session History Table Chronological Order Sort</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Verify pagination controls navigate between pages 1, 2, 3...</t>
+          <t>Table Pagination Control Navigation (1, 2, 3...)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verify page size dropdown switches between 10, 25, 50 rows per page</t>
+          <t>Page Size Dropdown Selection (10, 25, 50 Rows)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Verify search filter input filters sessions by date or session ID</t>
+          <t>Keyword Search Input Filter on Session Records</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Start Time column ascending/descending</t>
+          <t>Start Time Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Posture Score column ascending/descending</t>
+          <t>Posture Score Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Verify sorting session history table by Duration column ascending/descending</t>
+          <t>Session Duration Column Sort Ascending/Descending</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Verify clicking session row opens detailed session breakdown modal</t>
+          <t>Session Row Click Detailed Modal Drawer Trigger</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Verify session detail modal shows posture score heat map timeline</t>
+          <t>Session Detail Posture Heatmap Timeline View</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Verify session detail modal lists all recorded slouch events with timestamps</t>
+          <t>Session Slouch Log Event Timestamped Breakdown</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Verify session delete button opens confirmation modal</t>
+          <t>Session Deletion Confirmation Prompt Window</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verify confirming session deletion removes item from table and updates DB</t>
+          <t>Session Delete Execution DB Record Removal</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verify bulk selection checkboxes select multiple session records</t>
+          <t>Multi-Select Table Checkbox Bulk Action Handler</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verify bulk delete action removes all selected sessions simultaneously</t>
+          <t>Bulk Delete Batch API Call Processing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Verify session note editing inline within session history row</t>
+          <t>Inline Session Note Text Editing Capability</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Verify posture session tag filtering (Work, Gaming, Study)</t>
+          <t>Session Tag Category Filter (Work/Gaming/Study)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verify posture session snapshot image thumbnail preview on hover</t>
+          <t>Posture Snapshot Image Preview Modal Thumbnail</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Verify session duration formatting (e.g. 1h 24m 12s)</t>
+          <t>Formatted Session Duration String Parsing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Verify session history total record count footer accuracy</t>
+          <t>Session Table Total Record Count Footer Count</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Verify session export to JSON format download</t>
+          <t>Session Raw Metric Export to JSON File Format</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Verify session history table responsive horizontal scroll on mobile viewport</t>
+          <t>Session History Table Mobile Horizontal Scroll</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Verify session history empty search result state display</t>
+          <t>Empty Search Filter Results Placeholder Graphic</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verify session history network error retry button</t>
+          <t>API Network Error Fetch Retry Action Button</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verify session history print preview button opens browser print window</t>
+          <t>Table Print Preview Print-Friendly Media View</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verify session history column customizer checkbox dropdown</t>
+          <t>Column Customization Checkbox Visibility Dropdown</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verify posture alert settings page renders audio and visual toggles</t>
+          <t>Alert Settings Page Visual Audio Toggle Render</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verify posture slouch threshold slider (default 15 degrees)</t>
+          <t>Slouch Warning Threshold Slider Configuration</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Verify posture slouch delay alert timer setting (1s to 10s)</t>
+          <t>Slouch Trigger Delay Timer Selector (1s-10s)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Verify audio chime alert volume slider control</t>
+          <t>Alert Volume Master Gain Control Slider</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Verify audio chime tone selection dropdown (Bell, Beep, Chime)</t>
+          <t>Audio Chime Sound Selection Dropdown</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Verify test alert button triggers instant audio sample play</t>
+          <t>Instant Sample Audio Play Test Button</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Verify browser push notification toggle requests browser permission</t>
+          <t>Browser Push Notification Permission Trigger</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Verify email digest notification frequency dropdown (Daily, Weekly, Never)</t>
+          <t>Email Posture Summary Digest Frequency Select</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Verify desktop popup notification on continuous 30-minute slouch</t>
+          <t>30-Minute Continuous Slouch Desktop Popup</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verify break reminder alert after 45 minutes of continuous sitting</t>
+          <t>45-Minute Continuous Sitting Break Prompt</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verify ergonomic stretch prompt alert display on break reminder</t>
+          <t>Ergonomic Stretch Routine Modal Display</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verify alert history log table records all triggered posture warnings</t>
+          <t>Alert History Log Audit Table Generation</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verify clearing alert history log empties notification storage</t>
+          <t>Clear Alert History Log Purge Button Action</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Verify silent mode toggle disables all sound alerts during meetings</t>
+          <t>Meeting Silent Mode Notification Mute Switch</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Verify scheduled silent mode hours setup (e.g., 12:00 PM - 1:00 PM)</t>
+          <t>Scheduled Quiet Hours Time Range Configuration</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verify critical posture degradation SMS alert toggle</t>
+          <t>Critical Posture Breakdown SMS Alert Toggle</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verify alert sound file preloading on app initialization</t>
+          <t>Audio File Asset Preloading on App Launch</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verify notification badge count increments on new posture report</t>
+          <t>Top Navigation Bar Notification Badge Counter</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Verify clicking notification item redirects to session detail page</t>
+          <t>Notification Item Click Direct Session Reroute</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verify drag and drop zone accepts MP4 video files up to 100MB</t>
+          <t>Drag and Drop Upload Zone for 100MB MP4 Files</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verify file picker button opens native OS file selector dialog</t>
+          <t>File Picker OS Dialog Launch Button Action</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Verify error message when uploading unsupported file format (.txt, .exe)</t>
+          <t>Unsupported Extension (.exe/.txt) Error Block</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Verify error message when uploading video file exceeding 100MB limit</t>
+          <t>File Size Exceeded (&gt;100MB) Rejection Alert</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verify posture analysis video upload progress bar updates from 0% to 100%</t>
+          <t>Video Upload Percentage Progress Bar Indicator</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Verify video upload cancellation button aborts file upload HTTP request</t>
+          <t>Upload Cancellation HTTP Request Abort Action</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verify uploaded video frame extraction process status indicator</t>
+          <t>Frame Extraction Progress Status Spinner Screen</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verify posture analysis processing screen displays MediaPipe processing spinner</t>
+          <t>AI Video Posture Processing Pipeline Indicator</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Verify video posture analysis completion displays detailed AI report</t>
+          <t>Video AI Analysis Report Generation Render</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Verify posture angle timeline overlay rendered under video player</t>
+          <t>Posture Angle Timeline Video Player Overlay</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verify video playback controls (Play, Pause, Seek, Speed 0.5x-2x)</t>
+          <t>Video Player Playback Speed Controls (0.5x-2x)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step forward button during AI review</t>
+          <t>Video Frame Step Forward Precision Controls</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Verify video frame-by-frame step backward button during AI review</t>
+          <t>Video Frame Step Backward Precision Controls</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image upload for user avatar profile picture</t>
+          <t>Cloudinary Profile Avatar Photo Upload Action</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verify Cloudinary image cropping modal preview before saving avatar</t>
+          <t>Avatar Image Crop Modal Preview and Adjustment</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verify invalid image file upload rejection on avatar update</t>
+          <t>Corrupted Image File Upload Failure Rejection</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verify concurrent file upload handling queue (max 3 files)</t>
+          <t>Parallel File Upload Queue Management (Max 3)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verify server-side malware virus scan validation on uploaded media</t>
+          <t>Server Anti-Virus Security Scan Validation</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Verify automatic video thumbnail generation post-upload</t>
+          <t>Auto Video Keyframe Thumbnail Generation Test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verify posture video analysis report export to PDF</t>
+          <t>Video Posture Evaluation PDF Download Button</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verify uploaded file deletion button purges file from Cloudinary/S3</t>
+          <t>Uploaded Video File Permanent Deletion Action</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verify video analysis retry button on network transmission failure</t>
+          <t>Network Interruption Upload Retry Action Handler</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Verify video posture summary keyframe highlights gallery display</t>
+          <t>Video Keyframe Highlight Gallery Thumbnail Strip</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Verify video upload bandwidth throttling graceful degraded UX</t>
+          <t>Low Upload Bandwidth Degradation Graceful Mode</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Verify uploaded video aspect ratio preservation in HTML5 video tag</t>
+          <t>Aspect Ratio Preservation in HTML5 Video Tag</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verify PDF posture evaluation report layout and header formatting</t>
+          <t>PDF Posture Evaluation Report Layout Structure</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Verify PDF report includes user name, date range, and posture grade</t>
+          <t>PDF Report Header User Identity Metadata Render</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Verify PDF report embedded posture score trend chart image quality</t>
+          <t>PDF Report Embedded Trend Chart Image Clarity</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Verify PDF report ergonomic recommendations summary section</t>
+          <t>PDF Ergonomic Recommendation Summary Section</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Verify Excel raw posture telemetry export contains all 33 landmark columns</t>
+          <t>Excel 33 Pose Landmark Raw Coordinates Export</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verify Excel report includes multi-sheet tabs for Sessions, Summary, and Errors</t>
+          <t>Excel Workbook Multi-Sheet Tab Schema Structure</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verify CSV export file formatting with comma separation and UTF-8 encoding</t>
+          <t>CSV UTF-8 Formatted Data File Dispatch Action</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verify posture report email delivery feature sends PDF attachment</t>
+          <t>PDF Posture Report Email Delivery Dispatch</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verify custom date range filter applies to exported report data</t>
+          <t>Date Range Filter Application on Exported Data</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Verify automated weekly posture summary report email scheduling</t>
+          <t>Weekly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verify automated monthly posture summary report email scheduling</t>
+          <t>Monthly Automated Email Report Schedule Setup</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verify report generation loading overlay during PDF rendering</t>
+          <t>Report PDF Generation Rendering Loading Overlay</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verify print stylesheet (@media print) formats report page cleanly</t>
+          <t>@media print Print Stylesheet Layout Optimizer</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Verify posture health certificate download feature</t>
+          <t>Posture Health Certification PDF Certificate</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Verify posture data anonymized export for medical study consent</t>
+          <t>Anonymized Posture Medical Consent Export Action</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Verify report download failure retry prompt display</t>
+          <t>Report Download Error Retry Action Button Prompt</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verify password-protected PDF report export security option</t>
+          <t>Password-Encrypted PDF Report Protection Toggle</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verify corporate team posture aggregation report export for admins</t>
+          <t>Corporate Team Aggregated Posture Admin Report</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Verify export filename includes timestamp (e.g., Posture_Report_20260805.pdf)</t>
+          <t>Report Filename Timestamp Generator Syntax</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Verify top navigation bar links (Home, Calibration, Analytics, Reports, Settings)</t>
+          <t>Top Navbar Primary Destinations Routing Test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Verify active page route link highlighting in navbar</t>
+          <t>Active Page Link CSS State Highlight Visual</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verify sidebar toggle button expands and collapses side menu panel</t>
+          <t>Sidebar Collapsible Panel Toggle Button Action</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Verify sidebar navigation links match top navbar destinations</t>
+          <t>Sidebar Navigation Link Destination Matching</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Verify browser back button returns to previously visited route</t>
+          <t>Browser History Back Button Route Reversion</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Verify browser forward button navigates ahead correctly</t>
+          <t>Browser History Forward Navigation Flow Test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Verify browser page refresh (F5) maintains current URL state and session</t>
+          <t>Page Refresh (F5) URL State and Session Retention</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Verify 404 Page Not Found rendering for non-existent URL routes</t>
+          <t>404 Page Not Found Route Fallback Display</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Verify 404 page 'Return to Home' CTA button functionality</t>
+          <t>404 Page 'Return to Dashboard' Button Redirect</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verify breadcrumbs trail updating dynamically per nested sub-route</t>
+          <t>Dynamic Breadcrumbs Trail Update per Sub-Route</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verify footer quick links (About, Terms, Privacy, Support, API Docs)</t>
+          <t>Footer Terms and Privacy Policy Hyperlinks</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Verify sticky navigation bar remains pinned to top on page scroll</t>
+          <t>Sticky Navigation Bar Scroll Pinning Behavior</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown menu opens on avatar click</t>
+          <t>User Profile Avatar Header Menu Dropdown Open</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify user profile dropdown items (Profile, Billing, Settings, Logout)</t>
+          <t>Profile Dropdown Menu Option Redirects Test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+D' navigates to Dashboard</t>
+          <t>Keyboard Shortcut 'G+D' Dashboard Navigation</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify keyboard shortcut 'G+C' navigates to Calibration</t>
+          <t>Keyboard Shortcut 'G+C' Calibration Navigation</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify modal dialog close button (X) dismisses overlay</t>
+          <t>Modal Close Button (X) Click Dismiss Action</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify pressing ESC key closes open modal dialogs</t>
+          <t>Escape Key Press Modal Window Dismissal</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify clicking outside modal backdrop dismisses overlay</t>
+          <t>Backdrop Click Modal Dismissal Behavior Test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify page title (&lt;title&gt; tag) updates dynamically per route</t>
+          <t>Dynamic Page Document Title (&lt;title&gt;) Updates</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify dark mode theme toggle switches CSS background and text variables</t>
+          <t>Dark Theme Palette Variable CSS Class Switch</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify light mode theme toggle restores original high-contrast theme</t>
+          <t>Light Theme High-Contrast Mode Color Restoration</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify system color scheme preference (prefers-color-scheme) auto-detection</t>
+          <t>System Prefers-Color-Scheme Auto Detection</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify persistent theme preference saved in browser localStorage</t>
+          <t>Theme Preference Persistence in localStorage</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify high contrast mode toggle for visually impaired users</t>
+          <t>High Contrast Accessibility Toggle Switch</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify font size scaling controls (Small, Medium, Large, Extra Large)</t>
+          <t>Typography Font Size Scaling (Small to XL)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify screen reader ARIA labels on all interactive buttons</t>
+          <t>Interactive Component Screen Reader ARIA Labels</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify ARIA live regions announce posture status changes</t>
+          <t>ARIA Live Region Speech Output on Alert Push</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify keyboard focus indicator outline visible on TAB navigation</t>
+          <t>Keyboard TAB Focus Outline Indicator Highlight</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify tab order traverses web page elements in logical reading sequence</t>
+          <t>Logical TAB Key Navigation Order Sequence</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify color contrast ratio meets WCAG 2.1 AA benchmark (4.5:1 ratio)</t>
+          <t>WCAG 2.1 AA Color Contrast Ratio Verification</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify form input fields have explicit associated &lt;label&gt; elements</t>
+          <t>Form Input Field Associated &lt;label&gt; Tag Check</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify decorative images have empty alt text (alt='')</t>
+          <t>Decorative Image Empty Alt Text (alt='') Rule</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify functional images have descriptive alt text</t>
+          <t>Functional Icon Graphic Descriptive Alt Text</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify skipping to main content link works for screen readers</t>
+          <t>'Skip to Main Content' Accessibility Link Test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify interface animations pause when prefers-reduced-motion is active</t>
+          <t>Prefers-Reduced-Motion CSS Transition Freeze</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify tooltips accessible via keyboard focus hover</t>
+          <t>Keyboard Focus Hover Tooltip Popover Action</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify error state text is not conveyed by color alone (includes icons)</t>
+          <t>Multi-Sensory Error State Display (Icon plus Text)</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verify language attribute (&lt;html lang='en'&gt;) defined on document root</t>
+          <t>Document Root Language Attribute (&lt;html lang='en'&gt;)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verify semantic HTML5 tags (&lt;header&gt;, &lt;main&gt;, &lt;nav&gt;, &lt;footer&gt;) used throughout</t>
+          <t>Semantic HTML5 Structural Tags Layout Integrity</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Verify user profile name field trims leading and trailing whitespace</t>
+          <t>User Profile Display Name Whitespace Trimming</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Verify user profile name field max length restriction (50 chars)</t>
+          <t>Profile Display Name Character Cap (50 Chars)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Verify special character handling in user profile display name</t>
+          <t>Special Character Encoding in User Display Name</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verify email input field auto-complete attribute enabled</t>
+          <t>Email Address Field Browser Autocomplete Attribute</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Verify birthdate date picker restricts selection of future dates</t>
+          <t>Birthdate Selection Future Date Rejection Rule</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Verify height/weight numeric input fields reject negative numbers</t>
+          <t>Height and Weight Input Field Negative Number Rejection</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Verify height metric (cm) vs imperial (inches) unit toggle calculation</t>
+          <t>Height Units Switcher (Centimeters vs Inches)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Verify weight metric (kg) vs imperial (lbs) unit toggle calculation</t>
+          <t>Weight Units Switcher (Kilograms vs Pounds)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Verify posture target daily goal input field (range 15 to 480 mins)</t>
+          <t>Daily Posture Target Goal Range (15-480 Mins)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Verify real-time inline validation error display on blur event</t>
+          <t>Inline Real-Time Input Error Blur Validation</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Verify submit button disabled until all mandatory form fields are valid</t>
+          <t>Submit Button Disabled State on Invalid Inputs</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Verify clearing form button resets input fields to default values</t>
+          <t>Form Reset Clear Button Default State Restore</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Verify unsaved form changes warning modal on navigating away</t>
+          <t>Unsaved Form Changes Warning Navigation Alert</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Verify HTML form submission triggers on pressing Enter key inside text input</t>
+          <t>Enter Key Press Form Submission Event Launch</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verify text area character counter updates live as user types</t>
+          <t>Textarea Live Remaining Character Counter</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Verify password confirmation field matches new password input</t>
+          <t>Password Confirmation Match Validation Check</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Verify SQL injection string in input field is escaped properly</t>
+          <t>Input Escaping Security against SQL Injection</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Verify HTML code snippet input is escaped to prevent XSS execution</t>
+          <t>HTML Tag Encoding Security against XSS Payloads</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify form submission double-click prevention disables submit button</t>
+          <t>Submit Button Double-Click Action Prevention</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify desktop layout rendering at 1920x1080 resolution</t>
+          <t>1920x1080 Full HD Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Verify laptop layout rendering at 1366x768 resolution</t>
+          <t>1366x768 Standard Laptop Monitor Viewport Layout</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verify tablet viewport rendering at 768x1024 portrait resolution</t>
+          <t>768x1024 Tablet Portrait Mode Viewport Layout</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verify mobile viewport rendering at 375x812 iPhone X resolution</t>
+          <t>375x812 iPhone Mobile Screen Viewport Layout</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verify hamburger menu appears on screens below 768px width</t>
+          <t>Mobile Viewport Hamburger Navigation Menu Appears</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verify navigation menu collapses into slide-over drawer on mobile</t>
+          <t>Mobile Side-Drawer Navigation Transition</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Verify dashboard analytics grid wraps from 4 columns to 1 column on mobile</t>
+          <t>Dashboard 4-Column Grid Collapse to 1-Column</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verify live video stream canvas scales proportionally to screen width</t>
+          <t>Webcam Live Canvas Fluid Width Resizing</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Verify data tables horizontal scrollbar display on small viewports</t>
+          <t>Data Table Horizontal Scroll Bar Mobile Rendering</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verify touch drag gestures supported on mobile charts slider</t>
+          <t>Touch Screen Drag Gesture Support on Charts</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Verify Chrome browser latest version rendering stability</t>
+          <t>Google Chrome Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Verify Firefox browser latest version rendering stability</t>
+          <t>Mozilla Firefox Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Verify Safari browser latest version rendering stability</t>
+          <t>Apple Safari Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Verify Microsoft Edge browser latest version rendering stability</t>
+          <t>Microsoft Edge Latest Release Engine Stability</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verify MediaPipe WASM module loading across Chromium and WebKit browsers</t>
+          <t>MediaPipe WASM Engine Cross-Browser Loading</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verify WebGL 2.0 context initialization fallback on legacy hardware</t>
+          <t>WebGL Context Initialization Hardware Fallback</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Verify high DPI Retina display crisp image rendering</t>
+          <t>High DPI Retina Display Image Sharpness Check</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Verify viewport meta tag (width=device-width, initial-scale=1.0) present</t>
+          <t>Viewport Meta Tag Initial Scale Configuration</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Verify page content does not cause unintended horizontal overflow</t>
+          <t>Zero Horizontal Page Overflow Layout Inspection</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verify CSS grid and flexbox layout stability across browser engines</t>
+          <t>CSS Grid and Flexbox Layout Engine Parity</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Verify touch target minimum size of 44x44 pixels on mobile viewports</t>
+          <t>Minimum 44x44px Touch Target Size Verification</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Verify smooth CSS transition animations at 60 FPS</t>
+          <t>CSS Smooth Transition Animation 60 FPS Check</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Verify print CSS media query removes background images and navigation bars</t>
+          <t>@media print Navigation and Header Masking</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Verify web app manifest (manifest.json) PWA installability prompt</t>
+          <t>Web App Manifest PWA Installability Prompt</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
